--- a/03_Outputs/all/01_TablasDescriptivas/idx9_infnin_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx9_infnin_vr.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.535592581533732</v>
+        <v>2.535592581533733</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.886734367785</v>
+        <v>1.886734367784998</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.64961952998447</v>
+        <v>1.649619529984466</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.142532382401653</v>
+        <v>1.142532382401651</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9057983878300123</v>
+        <v>0.9057983878300117</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7434515264498469</v>
+        <v>0.7434515264498464</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.5350218190412833</v>
+        <v>0.5350218190412827</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.4237425185068647</v>
+        <v>0.4237425185068637</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>2.535592581533732</v>
+        <v>2.535592581533733</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>4.422326949318732</v>
+        <v>4.422326949318731</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>6.071946479303202</v>
+        <v>6.071946479303197</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>7.214478861704856</v>
+        <v>7.214478861704848</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>8.120277249534867</v>
+        <v>8.12027724953486</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>8.863728775984715</v>
+        <v>8.863728775984706</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>9.490328941873219</v>
+        <v>9.490328941873212</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>10.0253507609145</v>
+        <v>10.02535076091449</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>10.44909327942137</v>
+        <v>10.44909327942136</v>
       </c>
       <c r="C21">
         <v>9</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>11.00000000000001</v>
+        <v>10.99999999999999</v>
       </c>
       <c r="C23">
         <v>11</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>23.05084165030664</v>
+        <v>23.05084165030667</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>14.996541181677</v>
+        <v>14.99654118167697</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>10.38665802183321</v>
+        <v>10.3866580218332</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>8.234530798454653</v>
+        <v>8.234530798454655</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>6.75865024045315</v>
+        <v>6.758650240453153</v>
       </c>
       <c r="C29">
         <v>6</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>5.696365144440954</v>
+        <v>5.696365144440959</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>3.852204713698768</v>
+        <v>3.852204713698763</v>
       </c>
       <c r="C32">
         <v>9</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>3.649043900496065</v>
+        <v>3.649043900496069</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.359199013855183</v>
+        <v>1.359199013855185</v>
       </c>
       <c r="C34">
         <v>11</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>23.05084165030664</v>
+        <v>23.05084165030667</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>40.20297226653391</v>
+        <v>40.20297226653394</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>65.58617147004411</v>
+        <v>65.58617147004409</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>86.27571765339286</v>
+        <v>86.27571765339287</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>94.99175708564874</v>
+        <v>94.99175708564877</v>
       </c>
       <c r="C43">
         <v>9</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>98.64080098614481</v>
+        <v>98.64080098614482</v>
       </c>
       <c r="C44">
         <v>10</v>
